--- a/tmi2026.xlsx
+++ b/tmi2026.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ColoDiff: Integrating Dynamic Consistency With Content Awareness for Colonoscopy Video Generation (TMI 2026)</t>
+          <t>ColoDiff: Integrating Dynamic Consistency With Content Awareness for Colonoscopy Video Generation (TMI 2026, vol. 45)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
